--- a/exports/HDFCAMC_full_report.xlsx
+++ b/exports/HDFCAMC_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:U81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>4.55</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44579.55208333334</v>
+        <v>44580.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>1181.7</v>
+        <v>1153.3</v>
       </c>
       <c r="I2" t="n">
         <v>1170.5734</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.3</v>
+        <v>-4.65</v>
       </c>
       <c r="L2" t="n">
-        <v>3.47</v>
+        <v>5.13</v>
       </c>
       <c r="M2" t="n">
         <v>0.73</v>
       </c>
       <c r="N2" t="n">
-        <v>1.22</v>
+        <v>2.49</v>
       </c>
       <c r="O2" t="n">
         <v>3.16</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>5.36</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44593.55208333334</v>
+        <v>44594.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>1065.2</v>
+        <v>1101.4</v>
       </c>
       <c r="I3" t="n">
         <v>1097.846711729375</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K3" t="n">
-        <v>7.64</v>
+        <v>4.5</v>
       </c>
       <c r="L3" t="n">
         <v>2.58</v>
@@ -612,7 +647,7 @@
         <v>2.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.84</v>
+        <v>4.08</v>
       </c>
       <c r="O3" t="n">
         <v>-2.49</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44606.38541666666</v>
+        <v>44606.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>1048.1</v>
+        <v>1043.2</v>
       </c>
       <c r="I4" t="n">
         <v>1044.124249762839</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.84</v>
+        <v>-5.28</v>
       </c>
       <c r="L4" t="n">
         <v>6.88</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>5.04</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44635.55208333334</v>
+        <v>44636.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>1023.1</v>
+        <v>1060.3</v>
       </c>
       <c r="I5" t="n">
         <v>1044.207180299685</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>29</v>
+        <v>29.83333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>1.93</v>
+        <v>-1.64</v>
       </c>
       <c r="L5" t="n">
         <v>2.77</v>
@@ -726,7 +785,7 @@
         <v>2.38</v>
       </c>
       <c r="N5" t="n">
-        <v>2.79</v>
+        <v>3.59</v>
       </c>
       <c r="O5" t="n">
         <v>-1.3</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>7.42</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44645.55208333334</v>
+        <v>44648.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>1034.9</v>
+        <v>1008</v>
       </c>
       <c r="I6" t="n">
         <v>1014.992785094104</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.4</v>
+        <v>-4.93</v>
       </c>
       <c r="L6" t="n">
-        <v>3.92</v>
+        <v>5.68</v>
       </c>
       <c r="M6" t="n">
         <v>1.61</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>7.71</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44651.55208333334</v>
+        <v>44652.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>1029</v>
+        <v>1065.7</v>
       </c>
       <c r="I7" t="n">
         <v>1064.55613067709</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.08</v>
+        <v>-5.72</v>
       </c>
       <c r="L7" t="n">
-        <v>4.41</v>
+        <v>7.08</v>
       </c>
       <c r="M7" t="n">
-        <v>0.72</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>2.86</v>
+        <v>6.75</v>
       </c>
       <c r="O7" t="n">
         <v>-2.89</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,25 +971,25 @@
         <v>7.11</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44664.55208333334</v>
+        <v>44669.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>1058.4</v>
+        <v>1048.1</v>
       </c>
       <c r="I8" t="n">
         <v>1052.740415406153</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.68</v>
+        <v>-1.65</v>
       </c>
       <c r="L8" t="n">
-        <v>2.71</v>
+        <v>2.98</v>
       </c>
       <c r="M8" t="n">
-        <v>0.31</v>
+        <v>2.31</v>
       </c>
       <c r="N8" t="n">
         <v>1.79</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>5.94</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44708.55208333334</v>
+        <v>44711.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>867</v>
+        <v>878.8</v>
       </c>
       <c r="I9" t="n">
         <v>869.8851140842154</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K9" t="n">
-        <v>17.28</v>
+        <v>16.15</v>
       </c>
       <c r="L9" t="n">
         <v>1.96</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>6.2</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44728.38541666666</v>
+        <v>44728.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>861.7</v>
+        <v>854.8</v>
       </c>
       <c r="I10" t="n">
         <v>858.7042478593797</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.95</v>
+        <v>-2.73</v>
       </c>
       <c r="L10" t="n">
-        <v>2.12</v>
+        <v>2.96</v>
       </c>
       <c r="M10" t="n">
         <v>2.47</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>6.55</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44743.55208333334</v>
+        <v>44746.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>880.7</v>
+        <v>894.4</v>
       </c>
       <c r="I11" t="n">
         <v>889.3559459086563</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>15</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.03</v>
+        <v>-4.63</v>
       </c>
       <c r="L11" t="n">
-        <v>4.69</v>
+        <v>5.44</v>
       </c>
       <c r="M11" t="n">
         <v>1.05</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,25 +1247,25 @@
         <v>6.05</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44764.55208333334</v>
+        <v>44767.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>911.1</v>
+        <v>890</v>
       </c>
       <c r="I12" t="n">
         <v>895.3074301685707</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K12" t="n">
-        <v>1.87</v>
+        <v>-0.49</v>
       </c>
       <c r="L12" t="n">
         <v>1.59</v>
       </c>
       <c r="M12" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="N12" t="n">
         <v>2.3</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,25 +1316,25 @@
         <v>6.56</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44770.55208333334</v>
+        <v>44771.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>934.6</v>
+        <v>942.4</v>
       </c>
       <c r="I13" t="n">
         <v>939.3727597645831</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.01</v>
+        <v>-5.89</v>
       </c>
       <c r="L13" t="n">
-        <v>5.66</v>
+        <v>7.1</v>
       </c>
       <c r="M13" t="n">
-        <v>0.85</v>
+        <v>1.2</v>
       </c>
       <c r="N13" t="n">
         <v>2.57</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,25 +1385,25 @@
         <v>4.64</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44799.55208333334</v>
+        <v>44802.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>1003.1</v>
+        <v>985</v>
       </c>
       <c r="I14" t="n">
         <v>986.419363016563</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K14" t="n">
-        <v>6.44</v>
+        <v>4.52</v>
       </c>
       <c r="L14" t="n">
         <v>1.25</v>
       </c>
       <c r="M14" t="n">
-        <v>0.85</v>
+        <v>2.54</v>
       </c>
       <c r="N14" t="n">
         <v>2.98</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>5.49</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44852.55208333334</v>
+        <v>44853.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>929.7</v>
+        <v>949.2</v>
       </c>
       <c r="I15" t="n">
         <v>930.7955405039668</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>50.16666666666666</v>
+        <v>51</v>
       </c>
       <c r="K15" t="n">
-        <v>5.61</v>
+        <v>3.63</v>
       </c>
       <c r="L15" t="n">
         <v>1.53</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>4.95</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44916.55208333334</v>
+        <v>44917.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>1068.6</v>
+        <v>1049.5</v>
       </c>
       <c r="I16" t="n">
         <v>1053.273121442749</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>63.16666666666666</v>
+        <v>64</v>
       </c>
       <c r="K16" t="n">
-        <v>12.58</v>
+        <v>10.57</v>
       </c>
       <c r="L16" t="n">
         <v>3.03</v>
@@ -1353,7 +1544,7 @@
         <v>0.42</v>
       </c>
       <c r="N16" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="O16" t="n">
         <v>0.84</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>7.31</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45005.55208333334</v>
+        <v>45006.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>807.3</v>
+        <v>846.5</v>
       </c>
       <c r="I17" t="n">
         <v>840.706114182341</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>88.16666666666667</v>
+        <v>89</v>
       </c>
       <c r="K17" t="n">
-        <v>23.08</v>
+        <v>19.34</v>
       </c>
       <c r="L17" t="n">
         <v>2.75</v>
@@ -1410,7 +1613,7 @@
         <v>2.18</v>
       </c>
       <c r="N17" t="n">
-        <v>3.07</v>
+        <v>4.86</v>
       </c>
       <c r="O17" t="n">
         <v>-2.15</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>120</v>
+        <v>121</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>9.02</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45009.55208333334</v>
+        <v>45012.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>802.9</v>
+        <v>798.5</v>
       </c>
       <c r="I18" t="n">
         <v>800.3614105768377</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K18" t="n">
-        <v>-5.15</v>
+        <v>-5.67</v>
       </c>
       <c r="L18" t="n">
-        <v>6.19</v>
+        <v>7.29</v>
       </c>
       <c r="M18" t="n">
         <v>2.44</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>6.21</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45027.55208333334</v>
+        <v>45028.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>843.1</v>
+        <v>855.3</v>
       </c>
       <c r="I19" t="n">
         <v>847.6867115210376</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K19" t="n">
-        <v>-5.59</v>
+        <v>-7.11</v>
       </c>
       <c r="L19" t="n">
-        <v>6.01</v>
+        <v>7.36</v>
       </c>
       <c r="M19" t="n">
         <v>1.07</v>
       </c>
       <c r="N19" t="n">
-        <v>1.46</v>
+        <v>1.79</v>
       </c>
       <c r="O19" t="n">
         <v>0.5</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>4.71</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45042.38541666666</v>
+        <v>45042.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>841.1</v>
+        <v>834.7</v>
       </c>
       <c r="I20" t="n">
         <v>838.7258043791551</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.66</v>
+        <v>-2.41</v>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>2.51</v>
       </c>
       <c r="M20" t="n">
         <v>0.12</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>4.02</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45044.55208333334</v>
+        <v>45048.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>848.9</v>
+        <v>861.2</v>
       </c>
       <c r="I21" t="n">
         <v>860.2482859316465</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.7</v>
+        <v>-3.17</v>
       </c>
       <c r="L21" t="n">
-        <v>1.76</v>
+        <v>3.34</v>
       </c>
       <c r="M21" t="n">
         <v>0.53</v>
       </c>
       <c r="N21" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="O21" t="n">
         <v>-1.51</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>4.08</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45068.55208333334</v>
+        <v>45069.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>858.2</v>
+        <v>850.9</v>
       </c>
       <c r="I22" t="n">
         <v>857.4041783528735</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.35</v>
+        <v>-1.2</v>
       </c>
       <c r="L22" t="n">
         <v>2.73</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>4.43</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45071.55208333334</v>
+        <v>45072.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>847.5</v>
+        <v>890</v>
       </c>
       <c r="I23" t="n">
         <v>868.8895145621498</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4</v>
+        <v>-4.6</v>
       </c>
       <c r="L23" t="n">
-        <v>0.86</v>
+        <v>4.95</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="N23" t="n">
-        <v>1.29</v>
+        <v>5.07</v>
       </c>
       <c r="O23" t="n">
         <v>-1.14</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>6.81</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45090.55208333334</v>
+        <v>45091.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>948.7</v>
+        <v>918.4</v>
       </c>
       <c r="I24" t="n">
         <v>924.6074772834023</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K24" t="n">
-        <v>6.6</v>
+        <v>3.19</v>
       </c>
       <c r="L24" t="n">
         <v>4.78</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>6.52</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45096.55208333334</v>
+        <v>45097.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>908.6</v>
+        <v>976.6</v>
       </c>
       <c r="I25" t="n">
         <v>958.5208985182561</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K25" t="n">
-        <v>1.07</v>
+        <v>-6.34</v>
       </c>
       <c r="L25" t="n">
-        <v>4</v>
+        <v>7.68</v>
       </c>
       <c r="M25" t="n">
-        <v>1.22</v>
+        <v>7.59</v>
       </c>
       <c r="N25" t="n">
-        <v>0.11</v>
+        <v>11.42</v>
       </c>
       <c r="O25" t="n">
         <v>-2.06</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>7.41</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45141.55208333334</v>
+        <v>45142.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>1156.7</v>
+        <v>1145</v>
       </c>
       <c r="I26" t="n">
         <v>1152.238676939942</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K26" t="n">
-        <v>18.44</v>
+        <v>17.24</v>
       </c>
       <c r="L26" t="n">
         <v>2.3</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>7.59</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45147.55208333334</v>
+        <v>45148.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>1209.5</v>
+        <v>1238.4</v>
       </c>
       <c r="I27" t="n">
         <v>1225.18995918836</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K27" t="n">
-        <v>-5.63</v>
+        <v>-8.16</v>
       </c>
       <c r="L27" t="n">
-        <v>6.1</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="M27" t="n">
         <v>1.06</v>
       </c>
       <c r="N27" t="n">
-        <v>1.96</v>
+        <v>2.43</v>
       </c>
       <c r="O27" t="n">
         <v>-0.13</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>6.81</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45170.38541666666</v>
+        <v>45170.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>1173.3</v>
+        <v>1170.9</v>
       </c>
       <c r="I28" t="n">
         <v>1173.171434833856</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K28" t="n">
-        <v>-5.26</v>
+        <v>-5.45</v>
       </c>
       <c r="L28" t="n">
         <v>6.28</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>6.91</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45177.55208333334</v>
+        <v>45180.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>1218.4</v>
+        <v>1263.9</v>
       </c>
       <c r="I29" t="n">
         <v>1246.13600591153</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>7</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K29" t="n">
-        <v>-4.06</v>
+        <v>-7.94</v>
       </c>
       <c r="L29" t="n">
-        <v>4.43</v>
+        <v>7.98</v>
       </c>
       <c r="M29" t="n">
         <v>0.59</v>
       </c>
       <c r="N29" t="n">
-        <v>2.82</v>
+        <v>4.82</v>
       </c>
       <c r="O29" t="n">
         <v>-2.41</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>7.47</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45224.55208333334</v>
+        <v>45225.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>1350.5</v>
+        <v>1304</v>
       </c>
       <c r="I30" t="n">
         <v>1322.490450234339</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K30" t="n">
-        <v>6.85</v>
+        <v>3.17</v>
       </c>
       <c r="L30" t="n">
         <v>4.03</v>
@@ -2151,7 +2510,7 @@
         <v>1</v>
       </c>
       <c r="N30" t="n">
-        <v>2.71</v>
+        <v>3.27</v>
       </c>
       <c r="O30" t="n">
         <v>4.82</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>7.28</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45246.55208333334</v>
+        <v>45247.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>1350.5</v>
+        <v>1409.2</v>
       </c>
       <c r="I31" t="n">
         <v>1366.240378106929</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.57</v>
+        <v>-8.07</v>
       </c>
       <c r="L31" t="n">
-        <v>3.67</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="M31" t="n">
         <v>1.43</v>
       </c>
       <c r="N31" t="n">
-        <v>1.51</v>
+        <v>3.33</v>
       </c>
       <c r="O31" t="n">
         <v>-3.27</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>6.71</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45350.55208333334</v>
+        <v>45351.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>1838.8</v>
+        <v>1801.6</v>
       </c>
       <c r="I32" t="n">
         <v>1802.797197905885</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>103.1666666666667</v>
+        <v>104</v>
       </c>
       <c r="K32" t="n">
-        <v>30.49</v>
+        <v>27.85</v>
       </c>
       <c r="L32" t="n">
         <v>4.86</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>142</v>
+        <v>143</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>7.04</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45398.55208333334</v>
+        <v>45400.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>1793.3</v>
+        <v>1825.6</v>
       </c>
       <c r="I33" t="n">
         <v>1824.129103387557</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>47.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K33" t="n">
-        <v>0.46</v>
+        <v>-1.33</v>
       </c>
       <c r="L33" t="n">
         <v>3.34</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>5.92</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45419.55208333334</v>
+        <v>45420.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>1810.9</v>
+        <v>1792.3</v>
       </c>
       <c r="I34" t="n">
         <v>1803.102931421614</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.82</v>
       </c>
       <c r="L34" t="n">
         <v>5.34</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>5.8</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45427.55208333334</v>
+        <v>45428.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>1803.6</v>
+        <v>1838.3</v>
       </c>
       <c r="I35" t="n">
         <v>1828.873333265924</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.63</v>
+        <v>-2.57</v>
       </c>
       <c r="L35" t="n">
-        <v>1.39</v>
+        <v>2.9</v>
       </c>
       <c r="M35" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="N35" t="n">
-        <v>2.16</v>
+        <v>2.68</v>
       </c>
       <c r="O35" t="n">
         <v>-1.6</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>6.12</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45441.55208333334</v>
+        <v>45442.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>1870.1</v>
+        <v>1808.4</v>
       </c>
       <c r="I36" t="n">
         <v>1816.201451208229</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K36" t="n">
-        <v>1.73</v>
+        <v>-1.63</v>
       </c>
       <c r="L36" t="n">
-        <v>1.76</v>
+        <v>1.97</v>
       </c>
       <c r="M36" t="n">
-        <v>0.24</v>
+        <v>0.58</v>
       </c>
       <c r="N36" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="O36" t="n">
         <v>2.68</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>7.62</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45443.55208333334</v>
+        <v>45446.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>1873</v>
+        <v>1954.3</v>
       </c>
       <c r="I37" t="n">
         <v>1908.735882862281</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.57</v>
+        <v>-8.07</v>
       </c>
       <c r="L37" t="n">
-        <v>3.71</v>
+        <v>11.2</v>
       </c>
       <c r="M37" t="n">
-        <v>0.14</v>
+        <v>2.56</v>
       </c>
       <c r="N37" t="n">
-        <v>3.57</v>
+        <v>5.49</v>
       </c>
       <c r="O37" t="n">
         <v>-3.3</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>6.55</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>1975.8</v>
+        <v>1695.4</v>
       </c>
       <c r="I38" t="n">
         <v>1828.208292254058</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>1.1</v>
+        <v>-13.25</v>
       </c>
       <c r="L38" t="n">
-        <v>1.7</v>
+        <v>14.52</v>
       </c>
       <c r="M38" t="n">
-        <v>-0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>15.55</v>
       </c>
       <c r="O38" t="n">
         <v>5.49</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>19.58</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45454.55208333334</v>
+        <v>45455.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>1834.9</v>
+        <v>1904.8</v>
       </c>
       <c r="I39" t="n">
         <v>1896.290283274214</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K39" t="n">
-        <v>-8.23</v>
+        <v>-12.35</v>
       </c>
       <c r="L39" t="n">
         <v>15.53</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>10.56</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45495.55208333334</v>
+        <v>45496.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>1940.6</v>
+        <v>1887.7</v>
       </c>
       <c r="I40" t="n">
         <v>1933.406203355923</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K40" t="n">
-        <v>1.88</v>
+        <v>-0.9</v>
       </c>
       <c r="L40" t="n">
-        <v>4.03</v>
+        <v>6.63</v>
       </c>
       <c r="M40" t="n">
         <v>1.85</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>8.58</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45523.55208333334</v>
+        <v>45524.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>2012.5</v>
+        <v>2051.1</v>
       </c>
       <c r="I41" t="n">
         <v>2047.80429470989</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K41" t="n">
-        <v>-6.61</v>
+        <v>-8.66</v>
       </c>
       <c r="L41" t="n">
-        <v>8.27</v>
+        <v>9.41</v>
       </c>
       <c r="M41" t="n">
         <v>2.44</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>5.95</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45553.55208333334</v>
+        <v>45554.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>2128.4</v>
+        <v>2073.6</v>
       </c>
       <c r="I42" t="n">
         <v>2089.602814958496</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K42" t="n">
-        <v>3.77</v>
+        <v>1.1</v>
       </c>
       <c r="L42" t="n">
         <v>2.22</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>6.43</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45574.55208333334</v>
+        <v>45575.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>2099.6</v>
+        <v>2121.6</v>
       </c>
       <c r="I43" t="n">
         <v>2103.265391401953</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.25</v>
+        <v>-2.31</v>
       </c>
       <c r="L43" t="n">
         <v>5.17</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>6.15</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45587.38541666666</v>
+        <v>45587.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>2184.7</v>
+        <v>2173.5</v>
       </c>
       <c r="I44" t="n">
         <v>2174.262226282821</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K44" t="n">
-        <v>2.97</v>
+        <v>2.45</v>
       </c>
       <c r="L44" t="n">
         <v>1.64</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>6.5</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45632.55208333334</v>
+        <v>45635.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>2092.7</v>
+        <v>2150.5</v>
       </c>
       <c r="I45" t="n">
         <v>2117.286891416636</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>45</v>
+        <v>47.83333333333334</v>
       </c>
       <c r="K45" t="n">
-        <v>3.72</v>
+        <v>1.06</v>
       </c>
       <c r="L45" t="n">
         <v>0.99</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>6</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45643.55208333334</v>
+        <v>45644.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>2114.3</v>
+        <v>2092.7</v>
       </c>
       <c r="I46" t="n">
         <v>2094.417258397973</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.68</v>
+        <v>-2.69</v>
       </c>
       <c r="L46" t="n">
         <v>3.26</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>4.99</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45671.55208333334</v>
+        <v>45672.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>1872.5</v>
+        <v>1972.4</v>
       </c>
       <c r="I47" t="n">
         <v>1963.953042075239</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K47" t="n">
-        <v>10.52</v>
+        <v>5.75</v>
       </c>
       <c r="L47" t="n">
         <v>1.8</v>
@@ -3120,7 +3683,7 @@
         <v>1.76</v>
       </c>
       <c r="N47" t="n">
-        <v>2.86</v>
+        <v>3.56</v>
       </c>
       <c r="O47" t="n">
         <v>-0.72</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>10.8</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45681.55208333334</v>
+        <v>45684.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>1863.7</v>
+        <v>1792.8</v>
       </c>
       <c r="I48" t="n">
         <v>1833.930241604844</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K48" t="n">
-        <v>-5.51</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>6.47</v>
+        <v>9.9</v>
       </c>
       <c r="M48" t="n">
         <v>0.59</v>
       </c>
       <c r="N48" t="n">
-        <v>2.98</v>
+        <v>4.22</v>
       </c>
       <c r="O48" t="n">
         <v>3.56</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>8.82</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45688.38541666666</v>
+        <v>45688.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>1865.2</v>
+        <v>1921</v>
       </c>
       <c r="I49" t="n">
         <v>1912.951556057457</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K49" t="n">
-        <v>-4.04</v>
+        <v>-7.15</v>
       </c>
       <c r="L49" t="n">
-        <v>4.15</v>
+        <v>7.15</v>
       </c>
       <c r="M49" t="n">
         <v>1.61</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>8.880000000000001</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>1860.3</v>
+        <v>1753.2</v>
       </c>
       <c r="I50" t="n">
         <v>1779.939729695961</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K50" t="n">
-        <v>-3.16</v>
+        <v>-8.74</v>
       </c>
       <c r="L50" t="n">
-        <v>5.71</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="M50" t="n">
         <v>3.24</v>
       </c>
       <c r="N50" t="n">
-        <v>2.62</v>
+        <v>4.78</v>
       </c>
       <c r="O50" t="n">
         <v>6.23</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>11.61</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45721.38541666666</v>
+        <v>45721.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>1843.2</v>
+        <v>1853</v>
       </c>
       <c r="I51" t="n">
         <v>1844.168155514597</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K51" t="n">
-        <v>-5.13</v>
+        <v>-5.69</v>
       </c>
       <c r="L51" t="n">
         <v>7.61</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>6.03</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45751.38541666666</v>
+        <v>45751.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>1895.5</v>
+        <v>1874</v>
       </c>
       <c r="I52" t="n">
         <v>1876.305789019902</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>29.83333333333333</v>
+        <v>30</v>
       </c>
       <c r="K52" t="n">
-        <v>2.29</v>
+        <v>1.13</v>
       </c>
       <c r="L52" t="n">
         <v>5.13</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>6.79</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45756.55208333334</v>
+        <v>45758.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>1820.2</v>
+        <v>1933.2</v>
       </c>
       <c r="I53" t="n">
         <v>1916.905786738047</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>5</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K53" t="n">
-        <v>2.87</v>
+        <v>-3.16</v>
       </c>
       <c r="L53" t="n">
-        <v>1.36</v>
+        <v>3.32</v>
       </c>
       <c r="M53" t="n">
         <v>1.12</v>
       </c>
       <c r="N53" t="n">
-        <v>2.92</v>
+        <v>5</v>
       </c>
       <c r="O53" t="n">
         <v>-3.82</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>11.37</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45785.38541666666</v>
+        <v>45785.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>2103.5</v>
+        <v>2045.3</v>
       </c>
       <c r="I54" t="n">
         <v>2059.1165545281</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K54" t="n">
-        <v>8.81</v>
+        <v>5.8</v>
       </c>
       <c r="L54" t="n">
         <v>6.2</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>7.7</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45786.55208333334</v>
+        <v>45789.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>2053.1</v>
+        <v>2166.6</v>
       </c>
       <c r="I55" t="n">
         <v>2163.564230146006</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.38</v>
+        <v>-5.93</v>
       </c>
       <c r="L55" t="n">
-        <v>2.87</v>
+        <v>6.31</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="N55" t="n">
-        <v>0.38</v>
+        <v>6.05</v>
       </c>
       <c r="O55" t="n">
         <v>-3.6</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>8.59</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45826.55208333334</v>
+        <v>45827.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>2424</v>
+        <v>2387.8</v>
       </c>
       <c r="I56" t="n">
         <v>2397.872959706713</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K56" t="n">
-        <v>11.88</v>
+        <v>10.21</v>
       </c>
       <c r="L56" t="n">
         <v>3.57</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>7.05</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45834.55208333334</v>
+        <v>45835.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>2486.6</v>
+        <v>2524.8</v>
       </c>
       <c r="I57" t="n">
         <v>2523.644165790405</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K57" t="n">
-        <v>-4.14</v>
+        <v>-5.74</v>
       </c>
       <c r="L57" t="n">
-        <v>5.1</v>
+        <v>6.15</v>
       </c>
       <c r="M57" t="n">
         <v>1.26</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>5.58</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45881.38541666666</v>
+        <v>45881.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>2687.2</v>
+        <v>2668.6</v>
       </c>
       <c r="I58" t="n">
         <v>2675.604185579426</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>46</v>
+        <v>46.16666666666666</v>
       </c>
       <c r="K58" t="n">
-        <v>6.43</v>
+        <v>5.7</v>
       </c>
       <c r="L58" t="n">
         <v>3.41</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>4.97</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45887.38541666666</v>
+        <v>45887.55208333334</v>
       </c>
       <c r="H59" t="n">
-        <v>2789</v>
+        <v>2798.8</v>
       </c>
       <c r="I59" t="n">
         <v>2793.591724737253</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>5.833333333333333</v>
+        <v>6</v>
       </c>
       <c r="K59" t="n">
-        <v>-4.51</v>
+        <v>-4.88</v>
       </c>
       <c r="L59" t="n">
-        <v>4.6</v>
+        <v>5.08</v>
       </c>
       <c r="M59" t="n">
         <v>0.83</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>4.73</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45895.55208333334</v>
+        <v>45897.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>2814.4</v>
+        <v>2759.2</v>
       </c>
       <c r="I60" t="n">
         <v>2777.222046857814</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>8</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K60" t="n">
-        <v>0.5600000000000001</v>
+        <v>-1.41</v>
       </c>
       <c r="L60" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="M60" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="N60" t="n">
-        <v>2.28</v>
+        <v>2.95</v>
       </c>
       <c r="O60" t="n">
         <v>4.25</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>5.35</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45909.55208333334</v>
+        <v>45910.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>2764.5</v>
+        <v>2836.5</v>
       </c>
       <c r="I61" t="n">
         <v>2815.332326495836</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.19</v>
+        <v>-2.8</v>
       </c>
       <c r="L61" t="n">
-        <v>1.88</v>
+        <v>3.44</v>
       </c>
       <c r="M61" t="n">
         <v>1</v>
       </c>
       <c r="N61" t="n">
-        <v>2.43</v>
+        <v>2.69</v>
       </c>
       <c r="O61" t="n">
         <v>-2.95</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>5.22</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45926.38541666666</v>
+        <v>45926.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>2789</v>
+        <v>2759.6</v>
       </c>
       <c r="I62" t="n">
         <v>2783.823682184132</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K62" t="n">
-        <v>-1.67</v>
+        <v>-2.71</v>
       </c>
       <c r="L62" t="n">
-        <v>2.19</v>
+        <v>3.24</v>
       </c>
       <c r="M62" t="n">
         <v>0.46</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>4.26</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45944.55208333334</v>
+        <v>45945.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>2739.1</v>
+        <v>2810</v>
       </c>
       <c r="I63" t="n">
         <v>2790.872210789176</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>18</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K63" t="n">
-        <v>0.74</v>
+        <v>-1.83</v>
       </c>
       <c r="L63" t="n">
-        <v>1.28</v>
+        <v>2.02</v>
       </c>
       <c r="M63" t="n">
         <v>0.67</v>
       </c>
       <c r="N63" t="n">
-        <v>2.35</v>
+        <v>2.95</v>
       </c>
       <c r="O63" t="n">
         <v>-2.09</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>5.38</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45958.55208333334</v>
+        <v>45959.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>2771.4</v>
+        <v>2639.3</v>
       </c>
       <c r="I64" t="n">
         <v>2663.553774903241</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K64" t="n">
-        <v>-1.37</v>
+        <v>-6.07</v>
       </c>
       <c r="L64" t="n">
-        <v>4.12</v>
+        <v>7.92</v>
       </c>
       <c r="M64" t="n">
-        <v>0.2</v>
+        <v>4.27</v>
       </c>
       <c r="N64" t="n">
-        <v>1.46</v>
+        <v>4.63</v>
       </c>
       <c r="O64" t="n">
         <v>2.95</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>6.17</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46001.55208333334</v>
+        <v>46002.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>2552.3</v>
+        <v>2590.1</v>
       </c>
       <c r="I65" t="n">
         <v>2576.476623031647</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K65" t="n">
-        <v>3.3</v>
+        <v>1.86</v>
       </c>
       <c r="L65" t="n">
         <v>3.3</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>4.75</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46007.55208333334</v>
+        <v>46008.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>2523.7</v>
+        <v>2496.4</v>
       </c>
       <c r="I66" t="n">
         <v>2509.806627926495</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K66" t="n">
-        <v>-2.56</v>
+        <v>-3.62</v>
       </c>
       <c r="L66" t="n">
-        <v>3.16</v>
+        <v>4.16</v>
       </c>
       <c r="M66" t="n">
         <v>0.12</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>5.14</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46008.55208333334</v>
+        <v>46009.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>2494.4</v>
+        <v>2657.9</v>
       </c>
       <c r="I67" t="n">
         <v>2595.918537148116</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K67" t="n">
-        <v>0.08</v>
+        <v>-6.47</v>
       </c>
       <c r="L67" t="n">
-        <v>1.99</v>
+        <v>6.8</v>
       </c>
       <c r="M67" t="n">
-        <v>0.1</v>
+        <v>2.12</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>6.91</v>
       </c>
       <c r="O67" t="n">
         <v>-1.16</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>7.43</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46030.55208333334</v>
+        <v>46031.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>2523.7</v>
+        <v>2485.7</v>
       </c>
       <c r="I68" t="n">
         <v>2521.934984910026</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K68" t="n">
-        <v>-5.05</v>
+        <v>-6.48</v>
       </c>
       <c r="L68" t="n">
-        <v>5.49</v>
+        <v>7.16</v>
       </c>
       <c r="M68" t="n">
         <v>0.31</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,25 +5180,25 @@
         <v>5.14</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46036.55208333334</v>
+        <v>46038.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>2498.4</v>
+        <v>2552.8</v>
       </c>
       <c r="I69" t="n">
         <v>2534.976443925724</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K69" t="n">
-        <v>-0.51</v>
+        <v>-2.7</v>
       </c>
       <c r="L69" t="n">
-        <v>2.49</v>
+        <v>6.14</v>
       </c>
       <c r="M69" t="n">
-        <v>0.54</v>
+        <v>1.06</v>
       </c>
       <c r="N69" t="n">
         <v>2.53</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>5.23</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46044.55208333334</v>
+        <v>46045.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>2439.6</v>
+        <v>2410.1</v>
       </c>
       <c r="I70" t="n">
         <v>2419.266272378147</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K70" t="n">
-        <v>-4.43</v>
+        <v>-5.59</v>
       </c>
       <c r="L70" t="n">
         <v>5.92</v>
@@ -4431,7 +5270,7 @@
         <v>0.38</v>
       </c>
       <c r="N70" t="n">
-        <v>1.84</v>
+        <v>2.54</v>
       </c>
       <c r="O70" t="n">
         <v>1.45</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>6.75</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46055.38541666666</v>
+        <v>46055.55208333334</v>
       </c>
       <c r="H71" t="n">
-        <v>2467.9</v>
+        <v>2510.2</v>
       </c>
       <c r="I71" t="n">
         <v>2507.78989040031</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K71" t="n">
-        <v>-2.4</v>
+        <v>-4.15</v>
       </c>
       <c r="L71" t="n">
-        <v>4.15</v>
+        <v>4.78</v>
       </c>
       <c r="M71" t="n">
         <v>1.11</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>7.61</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46072.38541666666</v>
+        <v>46072.55208333334</v>
       </c>
       <c r="H72" t="n">
-        <v>2697</v>
+        <v>2671.6</v>
       </c>
       <c r="I72" t="n">
         <v>2696.465988076528</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>16.83333333333333</v>
+        <v>17</v>
       </c>
       <c r="K72" t="n">
-        <v>7.44</v>
+        <v>6.43</v>
       </c>
       <c r="L72" t="n">
         <v>2.16</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,28 +5456,28 @@
         <v>5.43</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>2294.5</v>
+        <v>2458.8</v>
       </c>
       <c r="I73" t="n">
         <v>2358.252766185006</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>47</v>
+        <v>47.83333333333334</v>
       </c>
       <c r="K73" t="n">
-        <v>14.12</v>
+        <v>7.97</v>
       </c>
       <c r="L73" t="n">
         <v>1.54</v>
       </c>
       <c r="M73" t="n">
-        <v>3.34</v>
+        <v>6.2</v>
       </c>
       <c r="N73" t="n">
-        <v>5.8</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="O73" t="n">
         <v>-2.81</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>3</v>
+      </c>
+      <c r="U73" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>9.609999999999999</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46153.55208333334</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="H74" t="n">
-        <v>2691.1</v>
+        <v>2606</v>
       </c>
       <c r="I74" t="n">
         <v>2659.605691263101</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K74" t="n">
-        <v>9.449999999999999</v>
+        <v>5.99</v>
       </c>
       <c r="L74" t="n">
         <v>3.23</v>
@@ -4659,7 +5546,7 @@
         <v>2.83</v>
       </c>
       <c r="N74" t="n">
-        <v>3.41</v>
+        <v>3.64</v>
       </c>
       <c r="O74" t="n">
         <v>8.710000000000001</v>
@@ -4668,7 +5555,19 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,28 +5594,28 @@
         <v>7.77</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H75" t="n">
-        <v>2459</v>
+        <v>2616.5</v>
       </c>
       <c r="I75" t="n">
         <v>2530.840916865656</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>34</v>
       </c>
       <c r="K75" t="n">
-        <v>5.64</v>
+        <v>-0.4</v>
       </c>
       <c r="L75" t="n">
         <v>5.51</v>
       </c>
       <c r="M75" t="n">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="N75" t="n">
-        <v>2.53</v>
+        <v>6.43</v>
       </c>
       <c r="O75" t="n">
         <v>-3.64</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>8.970000000000001</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46211.38541666666</v>
+        <v>46211.55208333334</v>
       </c>
       <c r="H76" t="n">
-        <v>2737</v>
+        <v>2657.8</v>
       </c>
       <c r="I76" t="n">
         <v>2677.833541278793</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K76" t="n">
-        <v>4.61</v>
+        <v>1.58</v>
       </c>
       <c r="L76" t="n">
         <v>4.49</v>
@@ -4782,7 +5693,19 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4809,19 +5732,19 @@
         <v>6.93</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46253.55208333334</v>
+        <v>46254.38541666666</v>
       </c>
       <c r="H77" t="n">
-        <v>2540.5</v>
+        <v>2599.1</v>
       </c>
       <c r="I77" t="n">
         <v>2565.069800017165</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>42</v>
+        <v>42.83333333333334</v>
       </c>
       <c r="K77" t="n">
-        <v>4.41</v>
+        <v>2.21</v>
       </c>
       <c r="L77" t="n">
         <v>4.97</v>
@@ -4839,7 +5762,19 @@
         <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,19 +5801,19 @@
         <v>4.78</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46261.38541666666</v>
+        <v>46261.55208333334</v>
       </c>
       <c r="H78" t="n">
-        <v>2585.8</v>
+        <v>2575</v>
       </c>
       <c r="I78" t="n">
         <v>2575.176347319183</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K78" t="n">
-        <v>-0.51</v>
+        <v>-0.93</v>
       </c>
       <c r="L78" t="n">
         <v>1.77</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4923,19 +5870,19 @@
         <v>4.52</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46309.55208333334</v>
+        <v>46310.38541666666</v>
       </c>
       <c r="H79" t="n">
-        <v>2292.1</v>
+        <v>2358.6</v>
       </c>
       <c r="I79" t="n">
         <v>2354.791405423141</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>48</v>
+        <v>48.83333333333334</v>
       </c>
       <c r="K79" t="n">
-        <v>10.99</v>
+        <v>8.4</v>
       </c>
       <c r="L79" t="n">
         <v>0.55</v>
@@ -4944,7 +5891,7 @@
         <v>1.59</v>
       </c>
       <c r="N79" t="n">
-        <v>1.75</v>
+        <v>5.19</v>
       </c>
       <c r="O79" t="n">
         <v>-3.68</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -4980,22 +5939,22 @@
         <v>6.89</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46317.55208333334</v>
+        <v>46318.38541666666</v>
       </c>
       <c r="H80" t="n">
-        <v>2280.3</v>
+        <v>2221.1</v>
       </c>
       <c r="I80" t="n">
         <v>2270.964078971399</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K80" t="n">
-        <v>-3.32</v>
+        <v>-5.83</v>
       </c>
       <c r="L80" t="n">
-        <v>4.27</v>
+        <v>5.94</v>
       </c>
       <c r="M80" t="n">
         <v>1.03</v>
@@ -5010,7 +5969,19 @@
         <v>1</v>
       </c>
       <c r="Q80" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S80" t="b">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>1</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -5061,6 +6032,12 @@
       <c r="Q81" t="n">
         <v>6</v>
       </c>
+      <c r="R81" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7163,7 +8140,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="6">
@@ -7173,7 +8150,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -7183,7 +8160,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>103.2</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8">
@@ -7193,7 +8170,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -7203,7 +8180,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29.1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
@@ -7213,7 +8190,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>45.2</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="11">
@@ -7223,7 +8200,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12">
@@ -7233,7 +8210,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -7243,7 +8220,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>77.2</v>
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -7253,7 +8230,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.69</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="15">
@@ -7263,7 +8240,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.29</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="16">
@@ -7273,7 +8250,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.07</v>
+        <v>-2.02</v>
       </c>
     </row>
     <row r="17">
@@ -7283,7 +8260,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30.49</v>
+        <v>27.85</v>
       </c>
     </row>
     <row r="18">
@@ -7293,7 +8270,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48.1</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="19">
@@ -7303,7 +8280,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.72</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="20">
@@ -7313,7 +8290,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.41</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="21">
@@ -7333,7 +8310,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23">
@@ -7343,7 +8320,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -7353,7 +8330,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.13</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="25">
@@ -7363,7 +8340,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.22</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="26">
@@ -7373,7 +8350,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.78</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="27">
@@ -7383,7 +8360,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.31</v>
+        <v>15.55</v>
       </c>
     </row>
     <row r="28">
@@ -7393,7 +8370,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29">
